--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannavila\Documents\Research\FittsLawR\fittsStudy\data_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfgon\Documents\Postodoc\FittsReaching\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A191274-C81E-48AA-9C08-9135B2A319FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB557EE-85F4-487A-8E70-D2253DAC8650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
+    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Order</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>a82582ab-6b34-49dc-9e48-a1c105fb614e</t>
+  </si>
+  <si>
+    <t>154464a6-deb4-43b5-aa10-3069ea48bd2b</t>
   </si>
 </sst>
 </file>
@@ -124,8 +127,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B7" totalsRowShown="0">
-  <autoFilter ref="A1:B7" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -533,6 +536,12 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
       <c r="J8">
         <v>3</v>
       </c>
@@ -662,7 +671,7 @@
       </c>
       <c r="B8">
         <f>+COUNTIF(Table2[Order],Total!A8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfgon\Documents\Postodoc\FittsReaching\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB557EE-85F4-487A-8E70-D2253DAC8650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21950B29-9424-4890-BE33-4AA8A74E81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
+    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Order</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>154464a6-deb4-43b5-aa10-3069ea48bd2b</t>
+  </si>
+  <si>
+    <t>4c1d71b2-2ffb-4a78-bf30-8997a4837565</t>
   </si>
 </sst>
 </file>
@@ -127,8 +130,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B8" totalsRowShown="0">
-  <autoFilter ref="A1:B8" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B9" totalsRowShown="0">
+  <autoFilter ref="A1:B9" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -553,6 +556,12 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
       <c r="J9">
         <v>8</v>
       </c>
@@ -680,7 +689,7 @@
       </c>
       <c r="B9">
         <f>+COUNTIF(Table2[Order],Total!A9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfgon\Documents\Postodoc\FittsReaching\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21950B29-9424-4890-BE33-4AA8A74E81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3246E383-1B37-4A85-85E1-23CF96D57946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
+    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Order</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>4c1d71b2-2ffb-4a78-bf30-8997a4837565</t>
+  </si>
+  <si>
+    <t>412143b2-afe0-413f-94fa-760dcb890417</t>
   </si>
 </sst>
 </file>
@@ -130,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B9" totalsRowShown="0">
-  <autoFilter ref="A1:B9" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B10" totalsRowShown="0">
+  <autoFilter ref="A1:B10" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -457,14 +460,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76CC67C-FE0E-4B01-B243-E31C793603DA}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.5703125" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -472,7 +475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -480,7 +483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -488,7 +491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -496,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -504,13 +507,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
+      <c r="I6">
+        <f>+J6*J7*J8</f>
+        <v>99</v>
+      </c>
       <c r="J6">
         <v>11</v>
       </c>
@@ -520,8 +527,11 @@
       <c r="L6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -537,8 +547,12 @@
       <c r="L7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="P7">
+        <f>+P6/J10</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -554,8 +568,12 @@
       <c r="L8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <f>+P6/PRODUCT(J6)</f>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -572,7 +590,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
       <c r="J10">
         <f>+PRODUCT(J6:J9)</f>
         <v>792</v>
@@ -586,13 +610,13 @@
         <v>864</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J11">
         <f>+J10*6</f>
         <v>4752</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F15">
         <v>0</v>
       </c>
@@ -625,7 +649,7 @@
       </c>
       <c r="B2">
         <f>+COUNTIF(Table2[Order],Total!A2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfgon\Documents\Postodoc\FittsReaching\data_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannavila\Documents\Research\FittsLawR\fittsStudy\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3246E383-1B37-4A85-85E1-23CF96D57946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8AA3D6-135B-46EA-9872-20239E975473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-1150" windowWidth="25820" windowHeight="13900" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
+    <workbookView xWindow="31485" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Order</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>412143b2-afe0-413f-94fa-760dcb890417</t>
+  </si>
+  <si>
+    <t>1356a579-de46-47ba-b38e-3059a66d9154</t>
   </si>
 </sst>
 </file>
@@ -133,8 +136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B10" totalsRowShown="0">
-  <autoFilter ref="A1:B10" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B11" totalsRowShown="0">
+  <autoFilter ref="A1:B11" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -528,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>7128</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -549,7 +552,7 @@
       </c>
       <c r="P7">
         <f>+P6/J10</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -570,7 +573,7 @@
       </c>
       <c r="P8">
         <f>+P6/PRODUCT(J6)</f>
-        <v>648</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -611,6 +614,12 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="J11">
         <f>+J10*6</f>
         <v>4752</v>
@@ -658,7 +667,7 @@
       </c>
       <c r="B3">
         <f>+COUNTIF(Table2[Order],Total!A3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannavila\Documents\Research\FittsLawR\fittsStudy\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8AA3D6-135B-46EA-9872-20239E975473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5131F3-40CB-4507-8153-A42972D089BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31485" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Order</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>1356a579-de46-47ba-b38e-3059a66d9154</t>
+  </si>
+  <si>
+    <t>ed68159d-c0ef-4c26-97c4-b9c56b320d3e</t>
   </si>
 </sst>
 </file>
@@ -136,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B11" totalsRowShown="0">
-  <autoFilter ref="A1:B11" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B12" totalsRowShown="0">
+  <autoFilter ref="A1:B12" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -531,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>7920</v>
+        <v>8712</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -552,7 +555,7 @@
       </c>
       <c r="P7">
         <f>+P6/J10</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -573,7 +576,7 @@
       </c>
       <c r="P8">
         <f>+P6/PRODUCT(J6)</f>
-        <v>720</v>
+        <v>792</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -623,6 +626,14 @@
       <c r="J11">
         <f>+J10*6</f>
         <v>4752</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -676,7 +687,7 @@
       </c>
       <c r="B4">
         <f>+COUNTIF(Table2[Order],Total!A4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1"/>
     </row>

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannavila\Documents\Research\FittsLawR\fittsStudy\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5131F3-40CB-4507-8153-A42972D089BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0795E1-86A7-48F7-9D2E-A5235F9ECDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Order</t>
   </si>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>ed68159d-c0ef-4c26-97c4-b9c56b320d3e</t>
+  </si>
+  <si>
+    <t>5086a4cd-6184-490c-a2fc-796872713589</t>
+  </si>
+  <si>
+    <t>49fdff37-48f2-4f74-9aad-eac94b7f7142</t>
+  </si>
+  <si>
+    <t>62698028-1622-42e0-8bee-71093a209362</t>
+  </si>
+  <si>
+    <t>1177595b-4d70-469a-9970-84df29e9666e</t>
   </si>
 </sst>
 </file>
@@ -139,8 +151,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B12" totalsRowShown="0">
-  <autoFilter ref="A1:B12" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
@@ -466,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76CC67C-FE0E-4B01-B243-E31C793603DA}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.5703125" customWidth="1"/>
@@ -534,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>8712</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -555,7 +567,7 @@
       </c>
       <c r="P7">
         <f>+P6/J10</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -576,7 +588,7 @@
       </c>
       <c r="P8">
         <f>+P6/PRODUCT(J6)</f>
-        <v>792</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -636,9 +648,39 @@
         <v>2</v>
       </c>
     </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
       <c r="F15">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -652,7 +694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EB2916-64B2-4D3E-9027-C8DA4CAC5A27}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
@@ -697,7 +739,7 @@
       </c>
       <c r="B5">
         <f>+COUNTIF(Table2[Order],Total!A5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,7 +748,7 @@
       </c>
       <c r="B6">
         <f>+COUNTIF(Table2[Order],Total!A6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -715,7 +757,7 @@
       </c>
       <c r="B7">
         <f>+COUNTIF(Table2[Order],Total!A7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -724,7 +766,7 @@
       </c>
       <c r="B8">
         <f>+COUNTIF(Table2[Order],Total!A8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -734,6 +776,12 @@
       <c r="B9">
         <f>+COUNTIF(Table2[Order],Total!A9)</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f>+SUM(B2:B9)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data_analysis/Participants.xlsx
+++ b/data_analysis/Participants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannavila\Documents\Research\FittsLawR\fittsStudy\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0795E1-86A7-48F7-9D2E-A5235F9ECDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7627DF76-EA29-4025-9BBC-A3EAFB8BD5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E312E5C9-68AC-4497-BDDB-8740A467E1C4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Order</t>
   </si>
@@ -87,14 +87,38 @@
     <t>62698028-1622-42e0-8bee-71093a209362</t>
   </si>
   <si>
-    <t>1177595b-4d70-469a-9970-84df29e9666e</t>
+    <t>6ea30fe1-e2e9-42c6-b0d4-d613d0b83620</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>lefthanded</t>
+  </si>
+  <si>
+    <t>a7bb3458-af72-4858-9ec8-2c1500215921</t>
+  </si>
+  <si>
+    <t>519b81d2-a1bd-409c-b301-55feb14af41d</t>
+  </si>
+  <si>
+    <t>eb327301-70b9-4e27-bbe4-7e716722ef9b</t>
+  </si>
+  <si>
+    <t>1ce7779e-eff2-478f-b326-6ae70fd6542d</t>
+  </si>
+  <si>
+    <t>9645c51a-9d84-4005-b976-9eaf6c717f09</t>
+  </si>
+  <si>
+    <t>45ef630c-2400-44bc-93df-dc646c2507ad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,10 +127,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF333333"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,15 +159,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -151,11 +197,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:B16" totalsRowShown="0">
-  <autoFilter ref="A1:B16" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}" name="Table2" displayName="Table2" ref="A1:C22" totalsRowShown="0">
+  <autoFilter ref="A1:C22" xr:uid="{90245000-5E62-4EA6-92CC-73A5CADB4F0B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{71FAC1A9-D0B1-4F4C-9433-2E468D8801B7}" name="Participant id" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{DB035266-98F4-40D8-AF2D-38F5FAD9EB9A}" name="Order"/>
+    <tableColumn id="3" xr3:uid="{A48AC03A-7340-4BF7-AE25-951AE45B991F}" name="lefthanded"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -478,55 +525,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76CC67C-FE0E-4B01-B243-E31C793603DA}">
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.5703125" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:16">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:16">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B6">
@@ -545,12 +596,12 @@
       <c r="L6">
         <v>9</v>
       </c>
-      <c r="P6">
-        <v>11088</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="P6" s="2">
+        <v>13464</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B7">
@@ -567,11 +618,11 @@
       </c>
       <c r="P7">
         <f>+P6/J10</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B8">
@@ -588,11 +639,11 @@
       </c>
       <c r="P8">
         <f>+P6/PRODUCT(J6)</f>
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B9">
@@ -608,8 +659,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:16">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B10">
@@ -628,8 +679,8 @@
         <v>864</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:16">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B11">
@@ -640,32 +691,32 @@
         <v>4752</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:16">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:16">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:16">
+      <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:16">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B15">
@@ -675,12 +726,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:16">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B16">
         <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -695,63 +797,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EB2916-64B2-4D3E-9027-C8DA4CAC5A27}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <f>+COUNTIF(Table2[Order],Total!A2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <f>+COUNTIF(Table2[Order],Total!A3)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
         <f>+COUNTIF(Table2[Order],Total!A4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
         <f>+COUNTIF(Table2[Order],Total!A5)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
         <f>+COUNTIF(Table2[Order],Total!A6)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -760,7 +862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -769,19 +871,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
         <f>+COUNTIF(Table2[Order],Total!A9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="B10">
         <f>+SUM(B2:B9)</f>
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
